--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2980004</v>
+        <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99156</v>
+        <v>99340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,37 +1243,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219875</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>jättetuja-beståndet, Öl</t>
+          <t>Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621410</v>
+        <v>621400</v>
       </c>
       <c r="R7" t="n">
-        <v>6346082</v>
+        <v>6346093</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,12 +1306,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2008-08-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2008-08-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,62 +1332,53 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Jan-Olof Petersson, Ulla-Britt Andersson, Göran Wendt, Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Anders Carlberg, Joakim Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2980004</t>
+          <t>https://artportalen.se/Sighting/137099682</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3927047</v>
+        <v>2980004</v>
       </c>
       <c r="B8" t="n">
-        <v>102240</v>
+        <v>99156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>219875</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1447,6 +1457,117 @@
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2980004</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3927047</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102240</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>jättetuja-beståndet, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>621410</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6346082</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2008-08-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2008-08-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Jan-Olof Petersson, Ulla-Britt Andersson, Göran Wendt, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/3927047</t>
         </is>
@@ -1461,6 +1582,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1265,11 +1265,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skäftekärr, Öl</t>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31558-2026 artfynd.xlsx
+++ b/artfynd/A 31558-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137099682</v>
       </c>
       <c r="B7" t="n">
-        <v>99416</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
